--- a/TestData/tasks.xlsx
+++ b/TestData/tasks.xlsx
@@ -1,21 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2484173\eclipse-workspace\TODOTrackerAutomation\TestData\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C2FE67A-7BCB-4234-93A4-EACA44AE7DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{21466CD3-1656-4605-9CD5-9DCFC658895B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{82CE6C83-7C0C-448D-BA79-FF2664CDC5B1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
+  <oleSize ref="A1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,6 +27,9 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -68,10 +67,10 @@
     <t>Low</t>
   </si>
   <si>
-    <t>Listening songs</t>
-  </si>
-  <si>
     <t>Study</t>
+  </si>
+  <si>
+    <t>travel</t>
   </si>
 </sst>
 </file>
@@ -499,7 +498,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -516,7 +515,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5">
         <v>1</v>
